--- a/backend/Bread_Orders.xlsx
+++ b/backend/Bread_Orders.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -463,7 +463,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -475,12 +475,88 @@
         <v>0</v>
       </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>